--- a/Kansas/WaterAllocation/KSwr_Allocation Schema Mapping to WaDE.xlsx
+++ b/Kansas/WaterAllocation/KSwr_Allocation Schema Mapping to WaDE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rjame\Documents\WSWC Documents\MappingStatesDataToWaDE2.0\Kansas\WaterAllocation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDEB11D-FF61-424D-859B-61B034EFACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B26CE90-7537-4703-BF94-C1B18B9C15F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="1692" windowWidth="23256" windowHeight="12456" tabRatio="714" activeTab="1" xr2:uid="{10FC1BAB-5472-410C-A2F0-85DCDF5389F8}"/>
+    <workbookView xWindow="30612" yWindow="2076" windowWidth="23256" windowHeight="12456" tabRatio="714" activeTab="5" xr2:uid="{10FC1BAB-5472-410C-A2F0-85DCDF5389F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping Notes" sheetId="10" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="838">
   <si>
     <t>Name</t>
   </si>
@@ -754,9 +754,6 @@
     <t>State:</t>
   </si>
   <si>
-    <t>Organizaitons:</t>
-  </si>
-  <si>
     <t>Data Links:</t>
   </si>
   <si>
@@ -1658,9 +1655,6 @@
   </si>
   <si>
     <t>The latitude and longitude need to be in decimal degrees based on the North American Datum of 1927 (NAD27).</t>
-  </si>
-  <si>
-    <t>https://geoportal.kgs.ku.edu/geohydro/wimas/index.cfm?CFID=70329&amp;CFTOKEN=76a0f9458d03b77b-4CFB47E3-D619-E415-5910FB0DDA91BD2F</t>
   </si>
   <si>
     <r>
@@ -1830,18 +1824,12 @@
     <t>KS</t>
   </si>
   <si>
-    <t>basin</t>
-  </si>
-  <si>
     <t>qty</t>
   </si>
   <si>
     <t>either Surface Water or Groundwater, see pre-processing</t>
   </si>
   <si>
-    <t>source</t>
-  </si>
-  <si>
     <t>basin name, see pre-processing</t>
   </si>
   <si>
@@ -2463,9 +2451,6 @@
     <t>Wyandotte</t>
   </si>
   <si>
-    <t>county</t>
-  </si>
-  <si>
     <t>priority_date</t>
   </si>
   <si>
@@ -2502,9 +2487,6 @@
     <t>bit</t>
   </si>
   <si>
-    <t>wrf_status</t>
-  </si>
-  <si>
     <t>wr_id</t>
   </si>
   <si>
@@ -2524,12 +2506,6 @@
   </si>
   <si>
     <t>Consumptive Use</t>
-  </si>
-  <si>
-    <t>Water quanity values also have an ID value where matching IDs have the same quanity value.</t>
-  </si>
-  <si>
-    <t>Water rights quanity values are split by wr_ID, pdiv_id, and quant_id.  Meaning some water rights will have different quanit_id values for similar / different pdiv_id.  This means we will have to remove a few entries as we group by the native water right ID vlaue (in this case wr_ID).</t>
   </si>
   <si>
     <t>Partial Completion Extended Time to Complete</t>
@@ -2598,6 +2574,33 @@
   </si>
   <si>
     <t>Use wr_id_x with 'http://geohydro.kgs.ku.edu/geohydro/wimas/water_right_list_direct.cfm?wr_id='</t>
+  </si>
+  <si>
+    <t>https://geohydro.kgs.ku.edu/geohydro/wimas/query_setup.cfm?CFID=6964114&amp;CFTOKEN=7c9c7b0cc38a2593-D0FF0719-BADF-C173-51EC4E3617FFF07A</t>
+  </si>
+  <si>
+    <t>Water quantity values also have an ID value where matching IDs have the same quantity value.</t>
+  </si>
+  <si>
+    <t>Water rights quantity values are split by wr_ID, pdiv_id, and quant_id.  Meaning some water rights will have different quanit_id values for similar / different pdiv_id.  This means we will have to remove a few entries as we group by the native water right ID value (in this case wr_ID).</t>
+  </si>
+  <si>
+    <t>Organizations:</t>
+  </si>
+  <si>
+    <t>default download will be the wimas with the location info. Need to click on the "summarize quantity" button to get a separate volume download.</t>
+  </si>
+  <si>
+    <t>source_of_supply</t>
+  </si>
+  <si>
+    <t>current_status_code</t>
+  </si>
+  <si>
+    <t>basin_num</t>
+  </si>
+  <si>
+    <t>county_code</t>
   </si>
 </sst>
 </file>
@@ -3388,7 +3391,7 @@
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3662,6 +3665,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3722,9 +3726,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3762,7 +3766,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3868,7 +3872,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4010,7 +4014,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4030,75 +4034,74 @@
         <v>236</v>
       </c>
       <c r="B1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="67" t="s">
-        <v>237</v>
+        <v>832</v>
       </c>
       <c r="B2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>539</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="73"/>
+      <c r="B6" s="95" t="s">
+        <v>833</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>813</v>
+        <v>830</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="67" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B15" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{65F7458D-9D58-4BA1-A8A5-E43ECAD50C35}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4205,7 +4208,7 @@
         <v>38</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="F4" s="43"/>
       <c r="G4" s="44"/>
@@ -4233,7 +4236,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="20"/>
@@ -4261,7 +4264,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F6" s="19"/>
       <c r="G6" s="20"/>
@@ -4289,7 +4292,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="20"/>
@@ -4317,7 +4320,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F8" s="19"/>
       <c r="G8" s="20"/>
@@ -4345,7 +4348,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="20"/>
@@ -4371,7 +4374,7 @@
         <v>38</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="20"/>
@@ -4399,7 +4402,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="F11" s="19"/>
       <c r="G11" s="20"/>
@@ -4427,7 +4430,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="20"/>
@@ -4556,7 +4559,7 @@
         <v>38</v>
       </c>
       <c r="E4" s="79" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="F4" s="43" t="s">
         <v>38</v>
@@ -4684,7 +4687,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>38</v>
@@ -4716,7 +4719,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>38</v>
@@ -4812,7 +4815,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>38</v>
@@ -4844,7 +4847,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>38</v>
@@ -4974,7 +4977,7 @@
         <v>38</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="F4" s="43" t="s">
         <v>38</v>
@@ -5006,7 +5009,7 @@
         <v>38</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>38</v>
@@ -5038,7 +5041,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>38</v>
@@ -5070,7 +5073,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="81" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>38</v>
@@ -5102,7 +5105,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>38</v>
@@ -5134,7 +5137,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>38</v>
@@ -5166,7 +5169,7 @@
         <v>38</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>38</v>
@@ -5198,7 +5201,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>38</v>
@@ -5230,7 +5233,7 @@
         <v>38</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>38</v>
@@ -5388,7 +5391,7 @@
         <v>38</v>
       </c>
       <c r="E4" s="74" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F4" s="75" t="s">
         <v>38</v>
@@ -5418,7 +5421,7 @@
         <v>38</v>
       </c>
       <c r="E5" s="71" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F5" s="71" t="s">
         <v>38</v>
@@ -5448,7 +5451,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="71" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F6" s="71" t="s">
         <v>38</v>
@@ -5508,13 +5511,13 @@
         <v>38</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F8" s="71" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G8" s="77" t="s">
-        <v>581</v>
+        <v>836</v>
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="17" t="s">
@@ -5541,10 +5544,10 @@
         <v>38</v>
       </c>
       <c r="F9" s="71" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G9" s="77" t="s">
-        <v>581</v>
+        <v>836</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="17">
@@ -5568,13 +5571,13 @@
         <v>20</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="F10" s="71" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G10" s="77" t="s">
-        <v>584</v>
+        <v>834</v>
       </c>
       <c r="H10" s="21"/>
       <c r="I10" s="17" t="s">
@@ -5700,7 +5703,7 @@
         <v>38</v>
       </c>
       <c r="E4" s="74" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F4" s="43" t="s">
         <v>38</v>
@@ -5730,7 +5733,7 @@
         <v>38</v>
       </c>
       <c r="E5" s="71" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>38</v>
@@ -5760,7 +5763,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>38</v>
@@ -5791,10 +5794,10 @@
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="23" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>792</v>
+        <v>837</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="19" t="s">
@@ -5848,7 +5851,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>38</v>
@@ -5876,7 +5879,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>38</v>
@@ -5906,7 +5909,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F11" s="23" t="s">
         <v>38</v>
@@ -5936,7 +5939,7 @@
         <v>38</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>38</v>
@@ -5969,10 +5972,10 @@
         <v>38</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="H13" s="22"/>
       <c r="I13" s="18" t="s">
@@ -5999,10 +6002,10 @@
         <v>38</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="H14" s="22"/>
       <c r="I14" s="18">
@@ -6026,7 +6029,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F15" s="23" t="s">
         <v>38</v>
@@ -6056,7 +6059,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F16" s="23" t="s">
         <v>38</v>
@@ -6074,7 +6077,7 @@
     </row>
     <row r="17" spans="1:10" s="49" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>16</v>
@@ -6086,7 +6089,7 @@
         <v>38</v>
       </c>
       <c r="E17" s="60" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="F17" s="33" t="s">
         <v>38</v>
@@ -6096,7 +6099,7 @@
       </c>
       <c r="H17" s="83"/>
       <c r="I17" s="84" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="J17" s="83"/>
     </row>
@@ -6112,7 +6115,7 @@
         <v>38</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>38</v>
@@ -6145,10 +6148,10 @@
         <v>38</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="H19" s="21"/>
       <c r="I19" s="18">
@@ -6172,7 +6175,7 @@
         <v>38</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F20" s="23" t="s">
         <v>38</v>
@@ -6232,7 +6235,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F22" s="23" t="s">
         <v>38</v>
@@ -6262,7 +6265,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F23" s="23" t="s">
         <v>38</v>
@@ -6532,7 +6535,7 @@
     </row>
     <row r="9" spans="1:10" s="49" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="49" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="B9" s="50" t="s">
         <v>34</v>
@@ -6544,7 +6547,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="F9" s="33"/>
       <c r="G9" s="46"/>
@@ -6566,7 +6569,7 @@
         <v>38</v>
       </c>
       <c r="E10" s="92" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="F10" s="68"/>
       <c r="G10" s="69"/>
@@ -6594,7 +6597,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="55" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="24"/>
@@ -6622,7 +6625,7 @@
         <v>38</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="24"/>
@@ -6650,7 +6653,7 @@
         <v>38</v>
       </c>
       <c r="E13" s="93" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="24"/>
@@ -6678,7 +6681,7 @@
         <v>38</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="42"/>
@@ -6706,7 +6709,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F15" s="33" t="s">
         <v>38</v>
@@ -6738,7 +6741,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F16" s="33" t="s">
         <v>38</v>
@@ -6770,7 +6773,7 @@
         <v>38</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F17" s="33" t="s">
         <v>38</v>
@@ -6802,7 +6805,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F18" s="33" t="s">
         <v>38</v>
@@ -6834,7 +6837,7 @@
         <v>38</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F19" s="33" t="s">
         <v>38</v>
@@ -6866,7 +6869,7 @@
         <v>38</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F20" s="33" t="s">
         <v>38</v>
@@ -6898,7 +6901,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F21" s="33" t="s">
         <v>38</v>
@@ -6930,7 +6933,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F22" s="33" t="s">
         <v>38</v>
@@ -6950,7 +6953,7 @@
     </row>
     <row r="23" spans="1:10" s="49" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="85" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="B23" s="50" t="s">
         <v>69</v>
@@ -6962,7 +6965,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F23" s="33" t="s">
         <v>38</v>
@@ -6997,10 +7000,10 @@
         <v>38</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>805</v>
+        <v>835</v>
       </c>
       <c r="H24" s="37" t="s">
         <v>38</v>
@@ -7029,10 +7032,10 @@
         <v>38</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="H25" s="37" t="s">
         <v>38</v>
@@ -7058,7 +7061,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F26" s="23" t="s">
         <v>38</v>
@@ -7093,10 +7096,10 @@
         <v>38</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="H27" s="37" t="s">
         <v>38</v>
@@ -7122,7 +7125,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F28" s="33" t="s">
         <v>38</v>
@@ -7154,7 +7157,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F29" s="33" t="s">
         <v>38</v>
@@ -7186,7 +7189,7 @@
         <v>38</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F30" s="33" t="s">
         <v>38</v>
@@ -7221,10 +7224,10 @@
         <v>38</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="H31" s="37" t="s">
         <v>38</v>
@@ -7233,12 +7236,12 @@
         <v>132</v>
       </c>
       <c r="J31" s="58" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="49" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="85" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B32" s="50" t="s">
         <v>69</v>
@@ -7253,10 +7256,10 @@
         <v>38</v>
       </c>
       <c r="F32" s="60" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G32" s="77" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="H32" s="86" t="s">
         <v>38</v>
@@ -7282,13 +7285,13 @@
         <v>38</v>
       </c>
       <c r="E33" s="57" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H33" s="37" t="s">
         <v>38</v>
@@ -7314,7 +7317,7 @@
         <v>38</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F34" s="33" t="s">
         <v>38</v>
@@ -7346,7 +7349,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F35" s="33" t="s">
         <v>38</v>
@@ -7378,7 +7381,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F36" s="33" t="s">
         <v>38</v>
@@ -7438,7 +7441,7 @@
         <v>38</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F38" s="33" t="s">
         <v>38</v>
@@ -7458,10 +7461,10 @@
     </row>
     <row r="39" spans="1:16" s="49" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="85" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>18</v>
@@ -7496,7 +7499,7 @@
         <v>38</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F40" s="33" t="s">
         <v>38</v>
@@ -7528,7 +7531,7 @@
         <v>38</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F41" s="33" t="s">
         <v>38</v>
@@ -7558,7 +7561,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F42" s="33" t="s">
         <v>38</v>
@@ -7590,7 +7593,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F43" s="33" t="s">
         <v>38</v>
@@ -7610,7 +7613,7 @@
     </row>
     <row r="44" spans="1:16" s="49" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>34</v>
@@ -7628,10 +7631,10 @@
         <v>38</v>
       </c>
       <c r="I44" s="62" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="J44" s="58" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
@@ -7654,7 +7657,7 @@
         <v>38</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F45" s="33" t="s">
         <v>38</v>
@@ -7686,7 +7689,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F46" s="33" t="s">
         <v>38</v>
@@ -7706,7 +7709,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="49" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="B47" s="50" t="s">
         <v>15</v>
@@ -7718,7 +7721,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="F47" s="33" t="s">
         <v>38</v>
@@ -7756,7 +7759,7 @@
         <v>38</v>
       </c>
       <c r="G48" s="46" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="H48" s="37" t="s">
         <v>38</v>
@@ -7826,18 +7829,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B1" s="78" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" t="s">
         <v>255</v>
-      </c>
-      <c r="B2" t="s">
-        <v>256</v>
       </c>
       <c r="C2" t="str">
         <f>""""&amp;A2&amp;""""&amp;" : "&amp;""""&amp;B2&amp;""""&amp;","</f>
@@ -7846,10 +7849,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" t="s">
         <v>257</v>
-      </c>
-      <c r="B3" t="s">
-        <v>258</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" ref="C3:C7" si="0">""""&amp;A3&amp;""""&amp;" : "&amp;""""&amp;B3&amp;""""&amp;","</f>
@@ -7858,10 +7861,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" t="s">
         <v>259</v>
-      </c>
-      <c r="B4" t="s">
-        <v>260</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
@@ -7870,10 +7873,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5" t="s">
         <v>261</v>
-      </c>
-      <c r="B5" t="s">
-        <v>262</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -7882,10 +7885,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" t="s">
         <v>263</v>
-      </c>
-      <c r="B6" t="s">
-        <v>264</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -7894,10 +7897,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" t="s">
         <v>265</v>
-      </c>
-      <c r="B7" t="s">
-        <v>266</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -7906,10 +7909,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -7917,7 +7920,7 @@
         <v>137</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" ref="C11:C12" si="1">""""&amp;A11&amp;""""&amp;" : "&amp;""""&amp;B11&amp;""""&amp;","</f>
@@ -7926,10 +7929,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12" t="s">
         <v>268</v>
-      </c>
-      <c r="B12" t="s">
-        <v>269</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="1"/>
@@ -7938,18 +7941,18 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B15" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" ref="C15:C28" si="2">""""&amp;A15&amp;""""&amp;" : "&amp;""""&amp;B15&amp;""""&amp;","</f>
@@ -7958,10 +7961,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B16" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="2"/>
@@ -7970,10 +7973,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B17" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="2"/>
@@ -7982,10 +7985,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="2"/>
@@ -7994,10 +7997,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B19" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="2"/>
@@ -8006,10 +8009,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B20" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="2"/>
@@ -8018,10 +8021,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B21" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="2"/>
@@ -8030,7 +8033,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B22" t="s">
         <v>131</v>
@@ -8042,10 +8045,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B23" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="2"/>
@@ -8054,10 +8057,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B24" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="2"/>
@@ -8066,10 +8069,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B25" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="2"/>
@@ -8078,10 +8081,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B26" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="2"/>
@@ -8090,10 +8093,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B27" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="2"/>
@@ -8102,10 +8105,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B28" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="2"/>
@@ -8114,15 +8117,15 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B30" s="78" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s">
         <v>107</v>
@@ -8134,10 +8137,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="3"/>
@@ -8146,18 +8149,18 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B33" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B35" s="78" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -8165,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -8173,7 +8176,7 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -8181,7 +8184,7 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -8189,15 +8192,15 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B42" s="78" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -8205,7 +8208,7 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -8213,7 +8216,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -8221,7 +8224,7 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -8229,7 +8232,7 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -8237,23 +8240,23 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B49" s="78" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" ref="C50:C78" si="4">""""&amp;A50&amp;""""&amp;" : "&amp;""""&amp;B50&amp;""""&amp;","</f>
@@ -8262,10 +8265,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B51" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="4"/>
@@ -8274,10 +8277,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="4"/>
@@ -8286,10 +8289,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B53" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="4"/>
@@ -8298,10 +8301,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="4"/>
@@ -8310,10 +8313,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="4"/>
@@ -8322,10 +8325,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B56" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="4"/>
@@ -8334,10 +8337,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="4"/>
@@ -8346,10 +8349,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="4"/>
@@ -8358,10 +8361,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B59" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="4"/>
@@ -8370,10 +8373,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B60" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="4"/>
@@ -8382,10 +8385,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B61" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="4"/>
@@ -8394,10 +8397,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="4"/>
@@ -8406,10 +8409,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B63" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="4"/>
@@ -8418,10 +8421,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B64" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="4"/>
@@ -8430,10 +8433,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B65" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" si="4"/>
@@ -8442,10 +8445,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B66" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="4"/>
@@ -8454,10 +8457,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B67" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="4"/>
@@ -8466,10 +8469,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B68" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="4"/>
@@ -8478,10 +8481,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B69" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="4"/>
@@ -8490,10 +8493,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B70" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="4"/>
@@ -8502,10 +8505,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="4"/>
@@ -8514,10 +8517,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="4"/>
@@ -8526,10 +8529,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="4"/>
@@ -8538,10 +8541,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="4"/>
@@ -8550,10 +8553,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="4"/>
@@ -8562,10 +8565,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="4"/>
@@ -8574,10 +8577,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="4"/>
@@ -8586,10 +8589,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="4"/>
@@ -8598,10 +8601,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B81" s="78" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -8609,7 +8612,7 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" ref="C82:C143" si="5">""""&amp;A82&amp;""""&amp;" : "&amp;""""&amp;B82&amp;""""&amp;","</f>
@@ -8621,7 +8624,7 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="5"/>
@@ -8633,7 +8636,7 @@
         <v>3</v>
       </c>
       <c r="B84" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="5"/>
@@ -8645,7 +8648,7 @@
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="5"/>
@@ -8657,7 +8660,7 @@
         <v>5</v>
       </c>
       <c r="B86" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" si="5"/>
@@ -8669,7 +8672,7 @@
         <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="5"/>
@@ -8681,7 +8684,7 @@
         <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="5"/>
@@ -8693,7 +8696,7 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" si="5"/>
@@ -8705,7 +8708,7 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="5"/>
@@ -8717,7 +8720,7 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="5"/>
@@ -8729,7 +8732,7 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="5"/>
@@ -8741,7 +8744,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="5"/>
@@ -8753,7 +8756,7 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="5"/>
@@ -8765,7 +8768,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="5"/>
@@ -8777,7 +8780,7 @@
         <v>15</v>
       </c>
       <c r="B96" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="5"/>
@@ -8789,7 +8792,7 @@
         <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="5"/>
@@ -8801,7 +8804,7 @@
         <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="5"/>
@@ -8813,7 +8816,7 @@
         <v>18</v>
       </c>
       <c r="B99" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="5"/>
@@ -8825,7 +8828,7 @@
         <v>19</v>
       </c>
       <c r="B100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="5"/>
@@ -8837,7 +8840,7 @@
         <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="5"/>
@@ -8849,7 +8852,7 @@
         <v>21</v>
       </c>
       <c r="B102" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="5"/>
@@ -8861,7 +8864,7 @@
         <v>22</v>
       </c>
       <c r="B103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="5"/>
@@ -8873,7 +8876,7 @@
         <v>23</v>
       </c>
       <c r="B104" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="5"/>
@@ -8885,7 +8888,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="5"/>
@@ -8897,7 +8900,7 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="5"/>
@@ -8909,7 +8912,7 @@
         <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="5"/>
@@ -8921,7 +8924,7 @@
         <v>27</v>
       </c>
       <c r="B108" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="5"/>
@@ -8933,7 +8936,7 @@
         <v>28</v>
       </c>
       <c r="B109" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="5"/>
@@ -8945,7 +8948,7 @@
         <v>29</v>
       </c>
       <c r="B110" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="5"/>
@@ -8957,7 +8960,7 @@
         <v>30</v>
       </c>
       <c r="B111" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="5"/>
@@ -8969,7 +8972,7 @@
         <v>31</v>
       </c>
       <c r="B112" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="5"/>
@@ -8981,7 +8984,7 @@
         <v>32</v>
       </c>
       <c r="B113" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="5"/>
@@ -8993,7 +8996,7 @@
         <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="5"/>
@@ -9005,7 +9008,7 @@
         <v>34</v>
       </c>
       <c r="B115" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="5"/>
@@ -9017,7 +9020,7 @@
         <v>35</v>
       </c>
       <c r="B116" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="5"/>
@@ -9029,7 +9032,7 @@
         <v>36</v>
       </c>
       <c r="B117" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="5"/>
@@ -9041,7 +9044,7 @@
         <v>37</v>
       </c>
       <c r="B118" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="5"/>
@@ -9053,7 +9056,7 @@
         <v>38</v>
       </c>
       <c r="B119" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="5"/>
@@ -9065,7 +9068,7 @@
         <v>39</v>
       </c>
       <c r="B120" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="5"/>
@@ -9077,7 +9080,7 @@
         <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="5"/>
@@ -9089,7 +9092,7 @@
         <v>41</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="5"/>
@@ -9101,7 +9104,7 @@
         <v>42</v>
       </c>
       <c r="B123" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="5"/>
@@ -9113,7 +9116,7 @@
         <v>43</v>
       </c>
       <c r="B124" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="5"/>
@@ -9125,7 +9128,7 @@
         <v>44</v>
       </c>
       <c r="B125" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="5"/>
@@ -9137,7 +9140,7 @@
         <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="5"/>
@@ -9149,7 +9152,7 @@
         <v>46</v>
       </c>
       <c r="B127" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="5"/>
@@ -9161,7 +9164,7 @@
         <v>47</v>
       </c>
       <c r="B128" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="5"/>
@@ -9173,7 +9176,7 @@
         <v>48</v>
       </c>
       <c r="B129" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" si="5"/>
@@ -9185,7 +9188,7 @@
         <v>49</v>
       </c>
       <c r="B130" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="5"/>
@@ -9197,7 +9200,7 @@
         <v>50</v>
       </c>
       <c r="B131" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" si="5"/>
@@ -9209,7 +9212,7 @@
         <v>51</v>
       </c>
       <c r="B132" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="5"/>
@@ -9221,7 +9224,7 @@
         <v>52</v>
       </c>
       <c r="B133" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="5"/>
@@ -9233,7 +9236,7 @@
         <v>53</v>
       </c>
       <c r="B134" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="5"/>
@@ -9245,7 +9248,7 @@
         <v>54</v>
       </c>
       <c r="B135" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="5"/>
@@ -9257,7 +9260,7 @@
         <v>55</v>
       </c>
       <c r="B136" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C136" t="str">
         <f t="shared" si="5"/>
@@ -9269,7 +9272,7 @@
         <v>56</v>
       </c>
       <c r="B137" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C137" t="str">
         <f t="shared" si="5"/>
@@ -9281,7 +9284,7 @@
         <v>57</v>
       </c>
       <c r="B138" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C138" t="str">
         <f t="shared" si="5"/>
@@ -9293,7 +9296,7 @@
         <v>58</v>
       </c>
       <c r="B139" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C139" t="str">
         <f t="shared" si="5"/>
@@ -9305,7 +9308,7 @@
         <v>59</v>
       </c>
       <c r="B140" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C140" t="str">
         <f t="shared" si="5"/>
@@ -9317,7 +9320,7 @@
         <v>60</v>
       </c>
       <c r="B141" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C141" t="str">
         <f t="shared" si="5"/>
@@ -9329,7 +9332,7 @@
         <v>61</v>
       </c>
       <c r="B142" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C142" t="str">
         <f t="shared" si="5"/>
@@ -9341,7 +9344,7 @@
         <v>62</v>
       </c>
       <c r="B143" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C143" t="str">
         <f t="shared" si="5"/>
@@ -9350,34 +9353,34 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B144" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B145" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B146" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B147" s="78" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
@@ -9385,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="B148" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
@@ -9393,7 +9396,7 @@
         <v>2</v>
       </c>
       <c r="B149" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
@@ -9401,7 +9404,7 @@
         <v>3</v>
       </c>
       <c r="B150" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
@@ -9409,7 +9412,7 @@
         <v>4</v>
       </c>
       <c r="B151" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -9417,7 +9420,7 @@
         <v>5</v>
       </c>
       <c r="B152" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
@@ -9425,7 +9428,7 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
@@ -9433,7 +9436,7 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
@@ -9441,7 +9444,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
@@ -9449,7 +9452,7 @@
         <v>9</v>
       </c>
       <c r="B156" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
@@ -9457,7 +9460,7 @@
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
@@ -9465,7 +9468,7 @@
         <v>11</v>
       </c>
       <c r="B158" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
@@ -9473,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
@@ -9481,7 +9484,7 @@
         <v>13</v>
       </c>
       <c r="B160" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
@@ -9489,7 +9492,7 @@
         <v>14</v>
       </c>
       <c r="B161" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
@@ -9497,7 +9500,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
@@ -9505,7 +9508,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
@@ -9513,7 +9516,7 @@
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
@@ -9521,7 +9524,7 @@
         <v>18</v>
       </c>
       <c r="B165" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
@@ -9529,7 +9532,7 @@
         <v>19</v>
       </c>
       <c r="B166" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
@@ -9537,7 +9540,7 @@
         <v>20</v>
       </c>
       <c r="B167" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
@@ -9545,7 +9548,7 @@
         <v>21</v>
       </c>
       <c r="B168" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
@@ -9553,7 +9556,7 @@
         <v>22</v>
       </c>
       <c r="B169" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
@@ -9561,7 +9564,7 @@
         <v>23</v>
       </c>
       <c r="B170" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
@@ -9569,7 +9572,7 @@
         <v>24</v>
       </c>
       <c r="B171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
@@ -9577,7 +9580,7 @@
         <v>25</v>
       </c>
       <c r="B172" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
@@ -9585,7 +9588,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
@@ -9593,7 +9596,7 @@
         <v>27</v>
       </c>
       <c r="B174" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
@@ -9601,7 +9604,7 @@
         <v>28</v>
       </c>
       <c r="B175" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
@@ -9609,7 +9612,7 @@
         <v>29</v>
       </c>
       <c r="B176" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
@@ -9617,7 +9620,7 @@
         <v>30</v>
       </c>
       <c r="B177" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
@@ -9625,7 +9628,7 @@
         <v>31</v>
       </c>
       <c r="B178" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
@@ -9633,7 +9636,7 @@
         <v>32</v>
       </c>
       <c r="B179" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
@@ -9641,7 +9644,7 @@
         <v>33</v>
       </c>
       <c r="B180" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
@@ -9649,7 +9652,7 @@
         <v>34</v>
       </c>
       <c r="B181" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
@@ -9657,7 +9660,7 @@
         <v>35</v>
       </c>
       <c r="B182" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
@@ -9665,15 +9668,15 @@
         <v>36</v>
       </c>
       <c r="B183" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B186" s="78" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
@@ -9681,7 +9684,7 @@
         <v>1</v>
       </c>
       <c r="B187" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
@@ -9689,7 +9692,7 @@
         <v>2</v>
       </c>
       <c r="B188" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
@@ -9697,7 +9700,7 @@
         <v>3</v>
       </c>
       <c r="B189" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
@@ -9705,7 +9708,7 @@
         <v>4</v>
       </c>
       <c r="B190" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
@@ -9713,7 +9716,7 @@
         <v>5</v>
       </c>
       <c r="B191" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
@@ -9721,7 +9724,7 @@
         <v>6</v>
       </c>
       <c r="B192" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
@@ -9729,7 +9732,7 @@
         <v>7</v>
       </c>
       <c r="B193" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
@@ -9737,7 +9740,7 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
@@ -9745,18 +9748,18 @@
         <v>9</v>
       </c>
       <c r="B195" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="78" t="s">
+        <v>535</v>
+      </c>
+      <c r="B198" s="78" t="s">
         <v>536</v>
       </c>
-      <c r="B198" s="78" t="s">
-        <v>537</v>
-      </c>
       <c r="C198" s="78" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
@@ -9764,10 +9767,10 @@
         <v>1</v>
       </c>
       <c r="B199" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C199" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
@@ -9775,10 +9778,10 @@
         <v>2</v>
       </c>
       <c r="B200" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C200" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -9786,10 +9789,10 @@
         <v>3</v>
       </c>
       <c r="B201" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C201" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -9797,10 +9800,10 @@
         <v>4</v>
       </c>
       <c r="B202" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C202" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -9808,10 +9811,10 @@
         <v>5</v>
       </c>
       <c r="B203" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C203" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
@@ -9819,10 +9822,10 @@
         <v>6</v>
       </c>
       <c r="B204" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C204" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
@@ -9830,10 +9833,10 @@
         <v>7</v>
       </c>
       <c r="B205" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C205" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
@@ -9841,10 +9844,10 @@
         <v>8</v>
       </c>
       <c r="B206" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C206" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
@@ -9852,18 +9855,18 @@
         <v>9</v>
       </c>
       <c r="B207" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C207" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B210" s="78" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
@@ -9871,7 +9874,7 @@
         <v>1</v>
       </c>
       <c r="B211" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
@@ -9879,7 +9882,7 @@
         <v>2</v>
       </c>
       <c r="B212" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
@@ -9887,15 +9890,15 @@
         <v>3</v>
       </c>
       <c r="B213" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B216" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
@@ -9903,7 +9906,7 @@
         <v>1</v>
       </c>
       <c r="B217" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
@@ -9911,7 +9914,7 @@
         <v>2</v>
       </c>
       <c r="B218" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
@@ -9919,7 +9922,7 @@
         <v>3</v>
       </c>
       <c r="B219" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
@@ -9927,7 +9930,7 @@
         <v>4</v>
       </c>
       <c r="B220" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
@@ -9935,7 +9938,7 @@
         <v>5</v>
       </c>
       <c r="B221" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
@@ -9943,7 +9946,7 @@
         <v>6</v>
       </c>
       <c r="B222" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
@@ -9951,7 +9954,7 @@
         <v>7</v>
       </c>
       <c r="B223" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
@@ -9959,7 +9962,7 @@
         <v>8</v>
       </c>
       <c r="B224" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
@@ -9967,7 +9970,7 @@
         <v>9</v>
       </c>
       <c r="B225" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
@@ -9975,7 +9978,7 @@
         <v>10</v>
       </c>
       <c r="B226" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
@@ -9983,7 +9986,7 @@
         <v>11</v>
       </c>
       <c r="B227" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
@@ -9991,7 +9994,7 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
@@ -9999,7 +10002,7 @@
         <v>13</v>
       </c>
       <c r="B229" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
@@ -10007,7 +10010,7 @@
         <v>14</v>
       </c>
       <c r="B230" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
@@ -10015,7 +10018,7 @@
         <v>15</v>
       </c>
       <c r="B231" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
@@ -10023,7 +10026,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
@@ -10031,7 +10034,7 @@
         <v>17</v>
       </c>
       <c r="B233" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
@@ -10039,7 +10042,7 @@
         <v>18</v>
       </c>
       <c r="B234" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
@@ -10047,7 +10050,7 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
@@ -10055,7 +10058,7 @@
         <v>20</v>
       </c>
       <c r="B236" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
@@ -10063,7 +10066,7 @@
         <v>21</v>
       </c>
       <c r="B237" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
@@ -10071,7 +10074,7 @@
         <v>22</v>
       </c>
       <c r="B238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
@@ -10079,7 +10082,7 @@
         <v>23</v>
       </c>
       <c r="B239" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
@@ -10087,7 +10090,7 @@
         <v>24</v>
       </c>
       <c r="B240" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
@@ -10095,7 +10098,7 @@
         <v>25</v>
       </c>
       <c r="B241" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
@@ -10103,7 +10106,7 @@
         <v>26</v>
       </c>
       <c r="B242" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
@@ -10111,7 +10114,7 @@
         <v>27</v>
       </c>
       <c r="B243" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
@@ -10119,7 +10122,7 @@
         <v>28</v>
       </c>
       <c r="B244" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
@@ -10127,7 +10130,7 @@
         <v>29</v>
       </c>
       <c r="B245" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
@@ -10135,7 +10138,7 @@
         <v>30</v>
       </c>
       <c r="B246" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
@@ -10143,7 +10146,7 @@
         <v>31</v>
       </c>
       <c r="B247" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
@@ -10151,7 +10154,7 @@
         <v>32</v>
       </c>
       <c r="B248" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
@@ -10159,7 +10162,7 @@
         <v>33</v>
       </c>
       <c r="B249" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
@@ -10167,7 +10170,7 @@
         <v>34</v>
       </c>
       <c r="B250" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
@@ -10175,7 +10178,7 @@
         <v>35</v>
       </c>
       <c r="B251" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
@@ -10183,7 +10186,7 @@
         <v>36</v>
       </c>
       <c r="B252" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
@@ -10191,7 +10194,7 @@
         <v>37</v>
       </c>
       <c r="B253" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
@@ -10199,7 +10202,7 @@
         <v>38</v>
       </c>
       <c r="B254" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
@@ -10207,7 +10210,7 @@
         <v>39</v>
       </c>
       <c r="B255" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
@@ -10215,7 +10218,7 @@
         <v>40</v>
       </c>
       <c r="B256" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
@@ -10223,7 +10226,7 @@
         <v>41</v>
       </c>
       <c r="B257" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
@@ -10231,7 +10234,7 @@
         <v>42</v>
       </c>
       <c r="B258" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
@@ -10239,7 +10242,7 @@
         <v>43</v>
       </c>
       <c r="B259" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
@@ -10247,7 +10250,7 @@
         <v>44</v>
       </c>
       <c r="B260" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
@@ -10255,7 +10258,7 @@
         <v>45</v>
       </c>
       <c r="B261" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
@@ -10263,7 +10266,7 @@
         <v>46</v>
       </c>
       <c r="B262" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
@@ -10271,7 +10274,7 @@
         <v>47</v>
       </c>
       <c r="B263" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
@@ -10279,7 +10282,7 @@
         <v>48</v>
       </c>
       <c r="B264" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
@@ -10287,7 +10290,7 @@
         <v>49</v>
       </c>
       <c r="B265" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
@@ -10295,7 +10298,7 @@
         <v>50</v>
       </c>
       <c r="B266" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
@@ -10303,7 +10306,7 @@
         <v>51</v>
       </c>
       <c r="B267" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
@@ -10311,7 +10314,7 @@
         <v>52</v>
       </c>
       <c r="B268" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
@@ -10319,7 +10322,7 @@
         <v>53</v>
       </c>
       <c r="B269" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
@@ -10327,7 +10330,7 @@
         <v>54</v>
       </c>
       <c r="B270" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
@@ -10335,7 +10338,7 @@
         <v>55</v>
       </c>
       <c r="B271" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
@@ -10343,7 +10346,7 @@
         <v>56</v>
       </c>
       <c r="B272" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
@@ -10351,7 +10354,7 @@
         <v>57</v>
       </c>
       <c r="B273" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
@@ -10359,7 +10362,7 @@
         <v>58</v>
       </c>
       <c r="B274" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
@@ -10367,7 +10370,7 @@
         <v>59</v>
       </c>
       <c r="B275" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
@@ -10375,7 +10378,7 @@
         <v>60</v>
       </c>
       <c r="B276" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
@@ -10383,7 +10386,7 @@
         <v>61</v>
       </c>
       <c r="B277" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
@@ -10391,7 +10394,7 @@
         <v>62</v>
       </c>
       <c r="B278" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
@@ -10399,7 +10402,7 @@
         <v>63</v>
       </c>
       <c r="B279" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
@@ -10407,7 +10410,7 @@
         <v>64</v>
       </c>
       <c r="B280" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
@@ -10415,7 +10418,7 @@
         <v>65</v>
       </c>
       <c r="B281" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
@@ -10423,7 +10426,7 @@
         <v>66</v>
       </c>
       <c r="B282" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
@@ -10431,7 +10434,7 @@
         <v>67</v>
       </c>
       <c r="B283" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
@@ -10439,7 +10442,7 @@
         <v>68</v>
       </c>
       <c r="B284" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
@@ -10447,7 +10450,7 @@
         <v>69</v>
       </c>
       <c r="B285" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
@@ -10455,7 +10458,7 @@
         <v>70</v>
       </c>
       <c r="B286" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
@@ -10463,7 +10466,7 @@
         <v>71</v>
       </c>
       <c r="B287" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
@@ -10471,7 +10474,7 @@
         <v>72</v>
       </c>
       <c r="B288" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -10479,7 +10482,7 @@
         <v>73</v>
       </c>
       <c r="B289" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -10487,7 +10490,7 @@
         <v>74</v>
       </c>
       <c r="B290" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -10495,7 +10498,7 @@
         <v>75</v>
       </c>
       <c r="B291" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -10503,7 +10506,7 @@
         <v>76</v>
       </c>
       <c r="B292" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -10511,7 +10514,7 @@
         <v>77</v>
       </c>
       <c r="B293" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
@@ -10519,23 +10522,23 @@
         <v>78</v>
       </c>
       <c r="B294" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="78" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B300" s="78" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B301" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C301" t="str">
         <f t="shared" ref="C301:C364" si="6">""""&amp;A301&amp;""""&amp;" : "&amp;""""&amp;B301&amp;""""&amp;","</f>
@@ -10545,10 +10548,10 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B302" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C302" t="str">
         <f t="shared" si="6"/>
@@ -10558,10 +10561,10 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B303" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C303" t="str">
         <f t="shared" si="6"/>
@@ -10571,10 +10574,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B304" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C304" t="str">
         <f t="shared" si="6"/>
@@ -10584,10 +10587,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B305" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C305" t="str">
         <f t="shared" si="6"/>
@@ -10597,10 +10600,10 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B306" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C306" t="str">
         <f t="shared" si="6"/>
@@ -10610,10 +10613,10 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B307" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C307" t="str">
         <f t="shared" si="6"/>
@@ -10623,10 +10626,10 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B308" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C308" t="str">
         <f t="shared" si="6"/>
@@ -10636,10 +10639,10 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B309" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C309" t="str">
         <f t="shared" si="6"/>
@@ -10649,10 +10652,10 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B310" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C310" t="str">
         <f t="shared" si="6"/>
@@ -10662,10 +10665,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B311" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C311" t="str">
         <f t="shared" si="6"/>
@@ -10675,10 +10678,10 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B312" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C312" t="str">
         <f t="shared" si="6"/>
@@ -10688,10 +10691,10 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B313" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C313" t="str">
         <f t="shared" si="6"/>
@@ -10701,10 +10704,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B314" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C314" t="str">
         <f t="shared" si="6"/>
@@ -10714,10 +10717,10 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B315" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C315" t="str">
         <f t="shared" si="6"/>
@@ -10727,10 +10730,10 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B316" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C316" t="str">
         <f t="shared" si="6"/>
@@ -10740,10 +10743,10 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B317" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C317" t="str">
         <f t="shared" si="6"/>
@@ -10753,10 +10756,10 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B318" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C318" t="str">
         <f t="shared" si="6"/>
@@ -10766,10 +10769,10 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B319" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C319" t="str">
         <f t="shared" si="6"/>
@@ -10779,10 +10782,10 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B320" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C320" t="str">
         <f t="shared" si="6"/>
@@ -10792,10 +10795,10 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B321" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C321" t="str">
         <f t="shared" si="6"/>
@@ -10805,10 +10808,10 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B322" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C322" t="str">
         <f t="shared" si="6"/>
@@ -10818,10 +10821,10 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B323" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C323" t="str">
         <f t="shared" si="6"/>
@@ -10831,10 +10834,10 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B324" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C324" t="str">
         <f t="shared" si="6"/>
@@ -10844,10 +10847,10 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B325" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C325" t="str">
         <f t="shared" si="6"/>
@@ -10857,10 +10860,10 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B326" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C326" t="str">
         <f t="shared" si="6"/>
@@ -10870,10 +10873,10 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B327" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C327" t="str">
         <f t="shared" si="6"/>
@@ -10883,10 +10886,10 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B328" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C328" t="str">
         <f t="shared" si="6"/>
@@ -10896,10 +10899,10 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B329" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C329" t="str">
         <f t="shared" si="6"/>
@@ -10909,10 +10912,10 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B330" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C330" t="str">
         <f t="shared" si="6"/>
@@ -10922,10 +10925,10 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B331" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="C331" t="str">
         <f t="shared" si="6"/>
@@ -10935,10 +10938,10 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B332" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C332" t="str">
         <f t="shared" si="6"/>
@@ -10948,10 +10951,10 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B333" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C333" t="str">
         <f t="shared" si="6"/>
@@ -10961,10 +10964,10 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B334" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C334" t="str">
         <f t="shared" si="6"/>
@@ -10974,10 +10977,10 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B335" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C335" t="str">
         <f t="shared" si="6"/>
@@ -10987,10 +10990,10 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B336" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C336" t="str">
         <f t="shared" si="6"/>
@@ -11000,10 +11003,10 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B337" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C337" t="str">
         <f t="shared" si="6"/>
@@ -11013,10 +11016,10 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B338" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C338" t="str">
         <f t="shared" si="6"/>
@@ -11026,10 +11029,10 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B339" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C339" t="str">
         <f t="shared" si="6"/>
@@ -11039,10 +11042,10 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B340" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C340" t="str">
         <f t="shared" si="6"/>
@@ -11052,10 +11055,10 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B341" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C341" t="str">
         <f t="shared" si="6"/>
@@ -11065,10 +11068,10 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B342" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C342" t="str">
         <f t="shared" si="6"/>
@@ -11078,10 +11081,10 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B343" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C343" t="str">
         <f t="shared" si="6"/>
@@ -11091,10 +11094,10 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B344" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C344" t="str">
         <f t="shared" si="6"/>
@@ -11104,10 +11107,10 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B345" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C345" t="str">
         <f t="shared" si="6"/>
@@ -11117,10 +11120,10 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B346" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C346" t="str">
         <f t="shared" si="6"/>
@@ -11130,10 +11133,10 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B347" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="C347" t="str">
         <f t="shared" si="6"/>
@@ -11143,10 +11146,10 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B348" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C348" t="str">
         <f t="shared" si="6"/>
@@ -11156,10 +11159,10 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B349" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C349" t="str">
         <f t="shared" si="6"/>
@@ -11169,10 +11172,10 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B350" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C350" t="str">
         <f t="shared" si="6"/>
@@ -11182,10 +11185,10 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B351" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C351" t="str">
         <f t="shared" si="6"/>
@@ -11195,10 +11198,10 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B352" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C352" t="str">
         <f t="shared" si="6"/>
@@ -11208,10 +11211,10 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B353" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C353" t="str">
         <f t="shared" si="6"/>
@@ -11221,10 +11224,10 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B354" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C354" t="str">
         <f t="shared" si="6"/>
@@ -11234,10 +11237,10 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B355" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C355" t="str">
         <f t="shared" si="6"/>
@@ -11247,10 +11250,10 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B356" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C356" t="str">
         <f t="shared" si="6"/>
@@ -11260,10 +11263,10 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B357" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C357" t="str">
         <f t="shared" si="6"/>
@@ -11273,10 +11276,10 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B358" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C358" t="str">
         <f t="shared" si="6"/>
@@ -11286,10 +11289,10 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B359" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C359" t="str">
         <f t="shared" si="6"/>
@@ -11299,10 +11302,10 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B360" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C360" t="str">
         <f t="shared" si="6"/>
@@ -11312,10 +11315,10 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B361" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C361" t="str">
         <f t="shared" si="6"/>
@@ -11325,10 +11328,10 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B362" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C362" t="str">
         <f t="shared" si="6"/>
@@ -11338,10 +11341,10 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B363" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C363" t="str">
         <f t="shared" si="6"/>
@@ -11351,10 +11354,10 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B364" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C364" t="str">
         <f t="shared" si="6"/>
@@ -11364,10 +11367,10 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B365" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C365" t="str">
         <f t="shared" ref="C365:C405" si="7">""""&amp;A365&amp;""""&amp;" : "&amp;""""&amp;B365&amp;""""&amp;","</f>
@@ -11377,10 +11380,10 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B366" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="C366" t="str">
         <f t="shared" si="7"/>
@@ -11390,10 +11393,10 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B367" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="C367" t="str">
         <f t="shared" si="7"/>
@@ -11403,10 +11406,10 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B368" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="C368" t="str">
         <f t="shared" si="7"/>
@@ -11416,10 +11419,10 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B369" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C369" t="str">
         <f t="shared" si="7"/>
@@ -11429,10 +11432,10 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B370" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C370" t="str">
         <f t="shared" si="7"/>
@@ -11442,10 +11445,10 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B371" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C371" t="str">
         <f t="shared" si="7"/>
@@ -11455,10 +11458,10 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B372" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C372" t="str">
         <f t="shared" si="7"/>
@@ -11468,10 +11471,10 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B373" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="C373" t="str">
         <f t="shared" si="7"/>
@@ -11481,10 +11484,10 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B374" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C374" t="str">
         <f t="shared" si="7"/>
@@ -11494,10 +11497,10 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B375" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C375" t="str">
         <f t="shared" si="7"/>
@@ -11507,10 +11510,10 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B376" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C376" t="str">
         <f t="shared" si="7"/>
@@ -11520,10 +11523,10 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B377" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C377" t="str">
         <f t="shared" si="7"/>
@@ -11533,10 +11536,10 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B378" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C378" t="str">
         <f t="shared" si="7"/>
@@ -11546,10 +11549,10 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B379" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C379" t="str">
         <f t="shared" si="7"/>
@@ -11559,10 +11562,10 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B380" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C380" t="str">
         <f t="shared" si="7"/>
@@ -11572,10 +11575,10 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B381" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C381" t="str">
         <f t="shared" si="7"/>
@@ -11585,10 +11588,10 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B382" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C382" t="str">
         <f t="shared" si="7"/>
@@ -11598,10 +11601,10 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B383" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C383" t="str">
         <f t="shared" si="7"/>
@@ -11611,10 +11614,10 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B384" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C384" t="str">
         <f t="shared" si="7"/>
@@ -11624,10 +11627,10 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B385" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C385" t="str">
         <f t="shared" si="7"/>
@@ -11637,10 +11640,10 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B386" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C386" t="str">
         <f t="shared" si="7"/>
@@ -11650,10 +11653,10 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B387" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C387" t="str">
         <f t="shared" si="7"/>
@@ -11663,10 +11666,10 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B388" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C388" t="str">
         <f t="shared" si="7"/>
@@ -11676,10 +11679,10 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B389" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C389" t="str">
         <f t="shared" si="7"/>
@@ -11689,10 +11692,10 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B390" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C390" t="str">
         <f t="shared" si="7"/>
@@ -11702,10 +11705,10 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B391" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C391" t="str">
         <f t="shared" si="7"/>
@@ -11715,10 +11718,10 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B392" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C392" t="str">
         <f t="shared" si="7"/>
@@ -11728,10 +11731,10 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B393" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C393" t="str">
         <f t="shared" si="7"/>
@@ -11741,10 +11744,10 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B394" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C394" t="str">
         <f t="shared" si="7"/>
@@ -11754,10 +11757,10 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B395" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C395" t="str">
         <f t="shared" si="7"/>
@@ -11767,10 +11770,10 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B396" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C396" t="str">
         <f t="shared" si="7"/>
@@ -11780,10 +11783,10 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B397" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C397" t="str">
         <f t="shared" si="7"/>
@@ -11793,10 +11796,10 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B398" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C398" t="str">
         <f t="shared" si="7"/>
@@ -11806,10 +11809,10 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B399" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C399" t="str">
         <f t="shared" si="7"/>
@@ -11819,10 +11822,10 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B400" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C400" t="str">
         <f t="shared" si="7"/>
@@ -11832,10 +11835,10 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B401" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C401" t="str">
         <f t="shared" si="7"/>
@@ -11845,10 +11848,10 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B402" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C402" t="str">
         <f t="shared" si="7"/>
@@ -11858,10 +11861,10 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B403" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C403" t="str">
         <f t="shared" si="7"/>
@@ -11871,10 +11874,10 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B404" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="C404" t="str">
         <f t="shared" si="7"/>
@@ -11884,10 +11887,10 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B405" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C405" t="str">
         <f t="shared" si="7"/>
